--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/observations-summary.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="79">
   <si>
     <t>Profile</t>
   </si>
@@ -53,13 +53,13 @@
     <t>MII PR Mikrobio Allgemeine Bestimmung</t>
   </si>
   <si>
-    <t>null#26436-6, null#laboratory, null#MB, null#26436-6, null#laboratory, null#MB, null#18725-2</t>
+    <t>null#laboratory, null#MB</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>LOINC#41852-5</t>
+    <t>LOINC#41852-5, LOINC#null</t>
   </si>
   <si>
     <t>dateTimeĵ</t>
@@ -77,7 +77,7 @@
     <t>MII PR Mikrobio Allgemeine Kultur</t>
   </si>
   <si>
-    <t>LOINC#11475-1</t>
+    <t>LOINC#11475-1, LOINC#null</t>
   </si>
   <si>
     <t>mii-pr-mikrobio-antigen-antikoerper-quantitativ</t>
@@ -86,6 +86,9 @@
     <t>MII PR Mikrobio Antigen Antikoerper Quantitativ</t>
   </si>
   <si>
+    <t>null#null</t>
+  </si>
+  <si>
     <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-antigen-antikoerper-quantitative-tests-loinc (extensible)</t>
   </si>
   <si>
@@ -107,7 +110,7 @@
     <t>MII PR Mikrobio Barlett Score</t>
   </si>
   <si>
-    <t>LOINC#75371-5</t>
+    <t>LOINC#75371-5, LOINC#null</t>
   </si>
   <si>
     <t>SNOMED CT#702661004</t>
@@ -152,7 +155,7 @@
     <t>MII PR Mikrobio Mikroskopie</t>
   </si>
   <si>
-    <t>LOINC#105059-0</t>
+    <t>LOINC#105059-0, LOINC#null</t>
   </si>
   <si>
     <t>mii-pr-mikrobio-molekulare-pathogenlast</t>
@@ -170,7 +173,7 @@
     <t>MII PR Mikrobio MRGN Klasse</t>
   </si>
   <si>
-    <t>LOINC#99780-9</t>
+    <t>LOINC#99780-9, LOINC#null</t>
   </si>
   <si>
     <t>mii-pr-mikrobio-nugent-score</t>
@@ -179,7 +182,7 @@
     <t>MII PR Mikrobio Nugent Score</t>
   </si>
   <si>
-    <t>LOINC#101433-1</t>
+    <t>LOINC#101433-1, LOINC#null</t>
   </si>
   <si>
     <t>mii-pr-mikrobio-resistenzkategorie-status</t>
@@ -501,16 +504,16 @@
         <v>14</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>18</v>
@@ -524,28 +527,28 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>25</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>18</v>
@@ -559,10 +562,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>13</v>
@@ -571,7 +574,7 @@
         <v>14</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>14</v>
@@ -589,15 +592,15 @@
         <v>14</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>13</v>
@@ -606,16 +609,16 @@
         <v>14</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -624,15 +627,15 @@
         <v>14</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>13</v>
@@ -641,16 +644,16 @@
         <v>14</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -664,10 +667,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>13</v>
@@ -676,16 +679,16 @@
         <v>14</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -694,15 +697,15 @@
         <v>14</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>13</v>
@@ -711,7 +714,7 @@
         <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>14</v>
@@ -734,10 +737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>13</v>
@@ -746,16 +749,16 @@
         <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -769,10 +772,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>13</v>
@@ -781,7 +784,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>14</v>
@@ -804,10 +807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>13</v>
@@ -816,7 +819,7 @@
         <v>14</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>14</v>
@@ -825,7 +828,7 @@
         <v>16</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -834,15 +837,15 @@
         <v>14</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>13</v>
@@ -851,10 +854,10 @@
         <v>14</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>16</v>
@@ -874,10 +877,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>13</v>
@@ -886,10 +889,10 @@
         <v>14</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>16</v>
@@ -909,10 +912,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>13</v>
@@ -921,10 +924,10 @@
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>16</v>
@@ -944,10 +947,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>13</v>
@@ -956,10 +959,10 @@
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>16</v>
@@ -979,10 +982,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>13</v>
@@ -991,16 +994,16 @@
         <v>14</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
@@ -1014,10 +1017,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -1026,10 +1029,10 @@
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>16</v>
@@ -1049,10 +1052,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
@@ -1061,10 +1064,10 @@
         <v>14</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>16</v>
